--- a/Pruebas acumuladas/ACUMULADO GENERAL.xlsx
+++ b/Pruebas acumuladas/ACUMULADO GENERAL.xlsx
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ28"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7586,6 +7586,2757 @@
         <v/>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>MISHELL ALEJANDRA HOYOS CIFUENTES</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>1014292246</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>MATEMÁTICAS</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AD29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AF29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AG29" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AH29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AI29" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AJ29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AK29" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AL29" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AM29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AN29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AO29" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AP29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ29" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AS29" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AT29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AU29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AW29" s="5">
+        <f>COUNTIF(J29:AV29,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX29" s="5">
+        <f>COUNTIF(J29:AV29,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY29" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ29" s="6">
+        <f>AW29/AY29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>AARON ALEJANDRO GALINDO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>1233488618</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>MATEMÁTICAS</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R30" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X30" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AD30" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE30" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AG30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AH30" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AI30" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AK30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AL30" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AM30" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AN30" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AO30" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ30" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AR30" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AS30" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AT30" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AU30" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AW30" s="5">
+        <f>COUNTIF(J30:AV30,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX30" s="5">
+        <f>COUNTIF(J30:AV30,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY30" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ30" s="6">
+        <f>AW30/AY30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>DILAN STIVEN SANCHEZ GAMEZ</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>1057919701</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>MATEMÁTICAS</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X31" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AD31" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AF31" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AG31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AH31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AI31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AK31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AL31" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AM31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AO31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AR31" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AS31" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AU31" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AW31" s="5">
+        <f>COUNTIF(J31:AV31,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX31" s="5">
+        <f>COUNTIF(J31:AV31,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY31" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ31" s="6">
+        <f>AW31/AY31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>EMILIANA AVILES TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>1034788543</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>MATEMÁTICAS</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="R32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Z32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AD32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE32" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AG32" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AH32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AI32" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AJ32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AK32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AL32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AM32" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AO32" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AP32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ32" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AR32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AS32" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AU32" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AW32" s="5">
+        <f>COUNTIF(J32:AV32,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX32" s="5">
+        <f>COUNTIF(J32:AV32,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY32" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ32" s="6">
+        <f>AW32/AY32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>JULIAN ESTEBAN ROJAS URREGO</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>1025076168</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>MATEMÁTICAS</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P33" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R33" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X33" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AE33" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AG33" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AI33" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AK33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AL33" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AM33" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AN33" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AO33" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AR33" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AS33" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AU33" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AW33" s="5">
+        <f>COUNTIF(J33:AV33,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX33" s="5">
+        <f>COUNTIF(J33:AV33,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY33" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ33" s="6">
+        <f>AW33/AY33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>NASHLY DANIELA BARRERA ZAMBRANO</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>1028877532</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>MATEMÁTICAS</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AD34" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE34" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AG34" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AI34" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AK34" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AL34" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AM34" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AN34" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AO34" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AP34" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AR34" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AS34" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AU34" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AW34" s="5">
+        <f>COUNTIF(J34:AV34,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX34" s="5">
+        <f>COUNTIF(J34:AV34,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY34" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ34" s="6">
+        <f>AW34/AY34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>EMMY SHANTHAL CABARCA MELO</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>1066097029</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>MATEMÁTICAS</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AB35" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AE35" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF35" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AG35" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AH35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AI35" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AK35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AL35" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AM35" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AN35" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AO35" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ35" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AR35" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AS35" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AU35" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AW35" s="5">
+        <f>COUNTIF(J35:AV35,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX35" s="5">
+        <f>COUNTIF(J35:AV35,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY35" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ35" s="6">
+        <f>AW35/AY35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>DAFNE LUCIANA GARCIA PIAMBA</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>1141355418</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>MATEMÁTICAS</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N36" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AD36" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE36" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF36" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AG36" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AI36" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AK36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AL36" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AM36" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AN36" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AO36" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ36" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AR36" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AS36" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AU36" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AW36" s="5">
+        <f>COUNTIF(J36:AV36,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX36" s="5">
+        <f>COUNTIF(J36:AV36,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY36" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ36" s="6">
+        <f>AW36/AY36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>NICOLAS STEBAN PALACIOS TIRADO</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>1233494561</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>MATEMÁTICAS</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P37" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R37" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X37" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Z37" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AD37" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE37" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AG37" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AI37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AJ37" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AK37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AL37" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AM37" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AO37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AP37" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ37" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AR37" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AS37" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AU37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV37" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AW37" s="5">
+        <f>COUNTIF(J37:AV37,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX37" s="5">
+        <f>COUNTIF(J37:AV37,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY37" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ37" s="6">
+        <f>AW37/AY37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>JOSEPH ALEJANDRO GONZALEZ MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>1025075979</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>MATEMÁTICAS</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P38" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R38" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V38" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X38" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AB38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AE38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AG38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AH38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AI38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AK38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AL38" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AM38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AO38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AR38" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AS38" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AU38" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AW38" s="5">
+        <f>COUNTIF(J38:AV38,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX38" s="5">
+        <f>COUNTIF(J38:AV38,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY38" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ38" s="6">
+        <f>AW38/AY38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>JUAN FELIPE PEDROZO AREVALO</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>1222209808</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>MATEMÁTICAS</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P39" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R39" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X39" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AB39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AD39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AE39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AG39" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AH39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AI39" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AK39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AL39" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AM39" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AO39" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AR39" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AS39" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AU39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV39" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AW39" s="5">
+        <f>COUNTIF(J39:AV39,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX39" s="5">
+        <f>COUNTIF(J39:AV39,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY39" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ39" s="6">
+        <f>AW39/AY39</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7597,7 +10348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ28"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -14632,6 +17383,2785 @@
       </c>
       <c r="AZ28" s="6">
         <f>AW28/AY28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>MISHELL ALEJANDRA HOYOS CIFUENTES</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>1014292246</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>LENGUAJE</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AB29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AD29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE29" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AF29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AG29" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AH29" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AI29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AJ29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AK29" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AL29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AM29" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AN29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AO29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AP29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AR29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AS29" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AT29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AU29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AW29" s="5">
+        <f>COUNTIF(J29:AV29,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX29" s="5">
+        <f>COUNTIF(J29:AV29,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY29" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ29" s="6">
+        <f>AW29/AY29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>AARON ALEJANDRO GALINDO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>1233488618</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>LENGUAJE</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V30" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AB30" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AD30" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE30" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AG30" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AH30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AI30" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AJ30" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AK30" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AL30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AM30" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AO30" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ30" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AR30" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AS30" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AT30" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AU30" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AW30" s="5">
+        <f>COUNTIF(J30:AV30,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX30" s="5">
+        <f>COUNTIF(J30:AV30,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY30" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ30" s="6">
+        <f>AW30/AY30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>DILAN STIVEN SANCHEZ GAMEZ</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>1057919701</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>LENGUAJE</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr"/>
+      <c r="P31" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AD31" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AG31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AH31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AI31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AK31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AL31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AM31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AO31" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AS31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AT31" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AU31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AV31" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AW31" s="5">
+        <f>COUNTIF(J31:AV31,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX31" s="5">
+        <f>COUNTIF(J31:AV31,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY31" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ31" s="6">
+        <f>AW31/AY31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>EMILIANA AVILES TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>1034788543</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>LENGUAJE</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AB32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AD32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE32" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AG32" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AH32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AI32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AJ32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AK32" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AL32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AM32" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AN32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AO32" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ32" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AS32" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AT32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AU32" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AV32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AW32" s="5">
+        <f>COUNTIF(J32:AV32,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX32" s="5">
+        <f>COUNTIF(J32:AV32,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY32" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ32" s="6">
+        <f>AW32/AY32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>JULIAN ESTEBAN ROJAS URREGO</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>1025076168</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>LENGUAJE</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V33" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X33" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AB33" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AD33" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE33" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AG33" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AI33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AJ33" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AK33" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AL33" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AM33" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AO33" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ33" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AS33" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AT33" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AU33" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AW33" s="5">
+        <f>COUNTIF(J33:AV33,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX33" s="5">
+        <f>COUNTIF(J33:AV33,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY33" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ33" s="6">
+        <f>AW33/AY33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>NASHLY DANIELA BARRERA ZAMBRANO</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>1028877532</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>LENGUAJE</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R34" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AB34" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AD34" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE34" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AG34" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AI34" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AK34" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AL34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AM34" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AO34" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ34" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AS34" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AU34" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AV34" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AW34" s="5">
+        <f>COUNTIF(J34:AV34,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX34" s="5">
+        <f>COUNTIF(J34:AV34,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY34" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ34" s="6">
+        <f>AW34/AY34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>EMMY SHANTHAL CABARCA MELO</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>1066097029</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>LENGUAJE</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AD35" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AG35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AH35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AI35" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AK35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AL35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AM35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AN35" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AO35" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ35" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AS35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AT35" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AU35" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AW35" s="5">
+        <f>COUNTIF(J35:AV35,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX35" s="5">
+        <f>COUNTIF(J35:AV35,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY35" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ35" s="6">
+        <f>AW35/AY35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>DAFNE LUCIANA GARCIA PIAMBA</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>1141355418</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>LENGUAJE</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R36" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AB36" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AD36" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AG36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AI36" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AK36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AL36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AM36" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AN36" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AO36" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ36" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AS36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AU36" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AV36" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AW36" s="5">
+        <f>COUNTIF(J36:AV36,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX36" s="5">
+        <f>COUNTIF(J36:AV36,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY36" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ36" s="6">
+        <f>AW36/AY36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>NICOLAS STEBAN PALACIOS TIRADO</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>1233494561</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>LENGUAJE</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AB37" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AE37" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AG37" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AI37" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AK37" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AL37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AM37" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AO37" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ37" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AS37" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AT37" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AU37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV37" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AW37" s="5">
+        <f>COUNTIF(J37:AV37,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX37" s="5">
+        <f>COUNTIF(J37:AV37,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY37" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ37" s="6">
+        <f>AW37/AY37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>JOSEPH ALEJANDRO GONZALEZ MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>1025075979</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>LENGUAJE</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V38" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X38" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AB38" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AD38" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AG38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AH38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AI38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AJ38" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AK38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AL38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AM38" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AN38" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AO38" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AS38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AT38" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AU38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AV38" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AW38" s="5">
+        <f>COUNTIF(J38:AV38,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX38" s="5">
+        <f>COUNTIF(J38:AV38,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY38" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ38" s="6">
+        <f>AW38/AY38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>JUAN FELIPE PEDROZO AREVALO</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>1222209808</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>LENGUAJE</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AB39" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AD39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AE39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AG39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AH39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AI39" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AK39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AL39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AM39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AN39" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AO39" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ39" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AR39" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AS39" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AT39" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AU39" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AV39" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AW39" s="5">
+        <f>COUNTIF(J39:AV39,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX39" s="5">
+        <f>COUNTIF(J39:AV39,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY39" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ39" s="6">
+        <f>AW39/AY39</f>
         <v/>
       </c>
     </row>
